--- a/data/trans_orig/P05B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P05B-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la calidad percibida del medioambiente de su barrio en 2007</t>
+          <t>Población según la calidad percibida del medioambiente de su barrio en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13693</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19160</t>
+          <t>17381</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>11304</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28364</t>
+          <t>28674</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>20050</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40831</t>
+          <t>41360</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46597</t>
+          <t>46063</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77015</t>
+          <t>77200</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61624</t>
+          <t>61612</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>95610</t>
+          <t>93769</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116847</t>
+          <t>115538</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>160872</t>
+          <t>160974</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>513231</t>
+          <t>514619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>557876</t>
+          <t>557600</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>483818</t>
+          <t>482873</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>531982</t>
+          <t>528692</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1012183</t>
+          <t>1012892</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1073901</t>
+          <t>1075549</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,86%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67233</t>
+          <t>66037</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100115</t>
+          <t>101230</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67586</t>
+          <t>65894</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103266</t>
+          <t>101010</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>141997</t>
+          <t>144913</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>189186</t>
+          <t>193244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>920</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8502</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11083</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,47 +1465,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>7933</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>3778</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>15246</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>7933</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>3714</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>14745</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>12098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30748</t>
+          <t>30305</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26156</t>
+          <t>27793</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50581</t>
+          <t>51962</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44454</t>
+          <t>42855</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74006</t>
+          <t>72975</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>145466</t>
+          <t>143855</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>194373</t>
+          <t>195062</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>138973</t>
+          <t>137780</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185070</t>
+          <t>184720</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>294626</t>
+          <t>298829</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>363149</t>
+          <t>363031</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>605672</t>
+          <t>609138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>669304</t>
+          <t>672582</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>615706</t>
+          <t>618995</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>678445</t>
+          <t>677747</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1246118</t>
+          <t>1245293</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1328773</t>
+          <t>1329969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,96%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109470</t>
+          <t>105457</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>155823</t>
+          <t>153965</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96094</t>
+          <t>95355</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137169</t>
+          <t>137907</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>215650</t>
+          <t>215436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>279506</t>
+          <t>279866</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>12634</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>799</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18493</t>
+          <t>17045</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20005</t>
+          <t>20101</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15316</t>
+          <t>15704</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33546</t>
+          <t>34671</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24730</t>
+          <t>23667</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48165</t>
+          <t>48701</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136071</t>
+          <t>138092</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>183590</t>
+          <t>181810</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>137396</t>
+          <t>137886</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>181516</t>
+          <t>181400</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>285551</t>
+          <t>286802</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>347919</t>
+          <t>349746</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>426880</t>
+          <t>427116</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>474518</t>
+          <t>476337</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>416800</t>
+          <t>416071</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>465186</t>
+          <t>465402</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>860168</t>
+          <t>858375</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>926281</t>
+          <t>928289</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39306</t>
+          <t>40328</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66311</t>
+          <t>68143</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43571</t>
+          <t>44196</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71947</t>
+          <t>72750</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89602</t>
+          <t>88470</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>129260</t>
+          <t>129530</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17735</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17792</t>
+          <t>18212</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12352</t>
+          <t>12462</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30631</t>
+          <t>29901</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24087</t>
+          <t>24118</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47264</t>
+          <t>45967</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>44526</t>
+          <t>45474</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>75075</t>
+          <t>73082</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>73992</t>
+          <t>73911</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>110700</t>
+          <t>111083</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>248726</t>
+          <t>250753</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>304736</t>
+          <t>303871</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>279511</t>
+          <t>278366</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>340973</t>
+          <t>340687</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>543550</t>
+          <t>547346</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>627052</t>
+          <t>626801</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>494820</t>
+          <t>499885</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>556313</t>
+          <t>560175</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>558328</t>
+          <t>558661</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>623333</t>
+          <t>624272</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1074970</t>
+          <t>1074080</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1162742</t>
+          <t>1161149</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,71%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>74154</t>
+          <t>72430</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>110706</t>
+          <t>108038</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56558</t>
+          <t>54058</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>90077</t>
+          <t>86488</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>137169</t>
+          <t>136911</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>188710</t>
+          <t>184218</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13287</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>33491</t>
+          <t>32611</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12486</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30367</t>
+          <t>30036</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>31124</t>
+          <t>30041</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>56991</t>
+          <t>58166</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>59146</t>
+          <t>58566</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>93036</t>
+          <t>95655</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>116870</t>
+          <t>116553</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>163127</t>
+          <t>160354</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>186355</t>
+          <t>185225</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>241382</t>
+          <t>243605</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>616984</t>
+          <t>621924</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>709963</t>
+          <t>712896</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>658784</t>
+          <t>657519</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>756055</t>
+          <t>752487</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1306870</t>
+          <t>1304224</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1440174</t>
+          <t>1437931</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2101105</t>
+          <t>2098637</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2206990</t>
+          <t>2206359</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2133817</t>
+          <t>2135263</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2243091</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4261901</t>
+          <t>4267314</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4419779</t>
+          <t>4424225</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,53%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>323548</t>
+          <t>318544</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>394242</t>
+          <t>391800</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>293599</t>
+          <t>293614</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>360756</t>
+          <t>361689</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>634305</t>
+          <t>635306</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>731274</t>
+          <t>733809</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la calidad percibida del medioambiente de su barrio en 2012</t>
+          <t>Población según la calidad percibida del medioambiente de su barrio en 2012 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>725</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4488,97 +4488,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1932</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5915</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>1932</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>7669</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>6382</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1932</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>5846</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20877</t>
+          <t>20717</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42548</t>
+          <t>42348</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38013</t>
+          <t>38235</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67334</t>
+          <t>67207</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63924</t>
+          <t>63125</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>99930</t>
+          <t>99047</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>500761</t>
+          <t>501393</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>547154</t>
+          <t>548242</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>479393</t>
+          <t>479467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>529513</t>
+          <t>529334</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1001018</t>
+          <t>998300</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1065571</t>
+          <t>1062491</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,98%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>124990</t>
+          <t>124130</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>168044</t>
+          <t>168968</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116194</t>
+          <t>115080</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>161031</t>
+          <t>158585</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>249844</t>
+          <t>251985</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>311384</t>
+          <t>313564</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13216</t>
+          <t>14608</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11979</t>
+          <t>11860</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19011</t>
+          <t>19906</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19682</t>
+          <t>19600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12482</t>
+          <t>13084</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32503</t>
+          <t>32202</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21739</t>
+          <t>21928</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48133</t>
+          <t>45943</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103868</t>
+          <t>104165</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>147426</t>
+          <t>149855</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>105547</t>
+          <t>108467</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>149391</t>
+          <t>152341</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>222144</t>
+          <t>220625</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>284669</t>
+          <t>285011</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>755918</t>
+          <t>756340</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>811464</t>
+          <t>813146</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>766411</t>
+          <t>762658</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>823065</t>
+          <t>820478</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1539412</t>
+          <t>1539829</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1620841</t>
+          <t>1619559</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,32%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68739</t>
+          <t>70625</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105699</t>
+          <t>108089</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62946</t>
+          <t>63757</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>100265</t>
+          <t>99757</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>141347</t>
+          <t>142110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>194160</t>
+          <t>192929</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8391</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22947</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14879</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12207</t>
+          <t>12441</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32730</t>
+          <t>31072</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90771</t>
+          <t>93623</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>134141</t>
+          <t>134627</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>99278</t>
+          <t>97937</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>143418</t>
+          <t>140608</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>201271</t>
+          <t>201108</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>260234</t>
+          <t>259531</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>500675</t>
+          <t>500941</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>555805</t>
+          <t>554063</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>528065</t>
+          <t>527070</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>580011</t>
+          <t>577559</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1044251</t>
+          <t>1048359</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1119321</t>
+          <t>1120447</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,11%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>82239</t>
+          <t>82596</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>121461</t>
+          <t>120759</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75739</t>
+          <t>75949</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>113182</t>
+          <t>112093</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>166548</t>
+          <t>167663</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>221820</t>
+          <t>220392</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13324</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10585</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28244</t>
+          <t>27440</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28852</t>
+          <t>30385</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25312</t>
+          <t>25019</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>50032</t>
+          <t>49328</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>174346</t>
+          <t>174019</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>225454</t>
+          <t>225527</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>219346</t>
+          <t>217077</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>274676</t>
+          <t>276161</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>410547</t>
+          <t>410333</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>488455</t>
+          <t>485974</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>639492</t>
+          <t>636606</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>695038</t>
+          <t>692004</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>684937</t>
+          <t>688114</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>748424</t>
+          <t>749019</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1342593</t>
+          <t>1341210</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1427920</t>
+          <t>1425471</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,94%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37362</t>
+          <t>36231</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64562</t>
+          <t>63618</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>43229</t>
+          <t>43186</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>74466</t>
+          <t>74593</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>88073</t>
+          <t>87428</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>127291</t>
+          <t>128348</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26820</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16878</t>
+          <t>17139</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15684</t>
+          <t>14894</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>36022</t>
+          <t>35986</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29616</t>
+          <t>30687</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>56504</t>
+          <t>57748</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>35611</t>
+          <t>34733</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>63130</t>
+          <t>63108</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>73189</t>
+          <t>71454</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>112494</t>
+          <t>110045</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>425803</t>
+          <t>422877</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>514047</t>
+          <t>508314</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>496541</t>
+          <t>503120</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>590583</t>
+          <t>593096</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>951511</t>
+          <t>953770</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1080125</t>
+          <t>1073676</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2450111</t>
+          <t>2458595</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2558390</t>
+          <t>2560733</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2520727</t>
+          <t>2516948</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2629679</t>
+          <t>2624898</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5000306</t>
+          <t>4999756</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5161233</t>
+          <t>5157851</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,17%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>347636</t>
+          <t>345977</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>418518</t>
+          <t>420491</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>330018</t>
+          <t>330838</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>401220</t>
+          <t>408657</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>695932</t>
+          <t>693919</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>806443</t>
+          <t>801413</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la calidad percibida del medioambiente de su barrio en 2016</t>
+          <t>Población según la calidad percibida del medioambiente de su barrio en 2016 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>10774</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>939</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14233</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>903</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>17453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21766</t>
+          <t>21579</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45729</t>
+          <t>45379</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29087</t>
+          <t>28757</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53449</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56501</t>
+          <t>56785</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>90870</t>
+          <t>92084</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>363845</t>
+          <t>363826</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>415146</t>
+          <t>416872</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>370345</t>
+          <t>370133</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>421870</t>
+          <t>424933</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>749081</t>
+          <t>754847</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>822150</t>
+          <t>828794</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,65%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>217435</t>
+          <t>217227</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>269165</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>203812</t>
+          <t>204932</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>256119</t>
+          <t>254871</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>438275</t>
+          <t>435235</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>507057</t>
+          <t>504218</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,51%</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>8637</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18319</t>
+          <t>17288</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26825</t>
+          <t>26450</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16737</t>
+          <t>17618</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38304</t>
+          <t>39846</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68947</t>
+          <t>69440</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>106438</t>
+          <t>106084</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74261</t>
+          <t>74900</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>111498</t>
+          <t>110788</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>153742</t>
+          <t>154152</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>208526</t>
+          <t>208178</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>647575</t>
+          <t>644383</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>708550</t>
+          <t>710049</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>640481</t>
+          <t>641510</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>702742</t>
+          <t>703694</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1303518</t>
+          <t>1302362</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1394445</t>
+          <t>1394589</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,66%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>217511</t>
+          <t>214825</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>273892</t>
+          <t>273978</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>232886</t>
+          <t>229104</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>285952</t>
+          <t>285941</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>464938</t>
+          <t>463146</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>543941</t>
+          <t>544916</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>9190</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>6384</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11365</t>
+          <t>11370</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>17620</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15886</t>
+          <t>15884</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35940</t>
+          <t>36196</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22448</t>
+          <t>21922</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46645</t>
+          <t>45362</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97237</t>
+          <t>93808</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>138921</t>
+          <t>138262</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>97725</t>
+          <t>97071</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>138520</t>
+          <t>137204</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>204287</t>
+          <t>205483</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>260227</t>
+          <t>261682</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,98%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>435150</t>
+          <t>436006</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>492194</t>
+          <t>491424</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>437343</t>
+          <t>434407</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>492743</t>
+          <t>489921</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>889204</t>
+          <t>889256</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>966854</t>
+          <t>966259</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,69%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>144200</t>
+          <t>143439</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>190774</t>
+          <t>192309</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>151176</t>
+          <t>152872</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>202247</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>309514</t>
+          <t>309026</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>375978</t>
+          <t>375986</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9932</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2589</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13610</t>
+          <t>14217</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17924</t>
+          <t>17666</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15444</t>
+          <t>15709</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37751</t>
+          <t>37233</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23173</t>
+          <t>24551</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48593</t>
+          <t>48468</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>156079</t>
+          <t>156907</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>205384</t>
+          <t>203977</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>172203</t>
+          <t>171230</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>224703</t>
+          <t>224167</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>342829</t>
+          <t>339454</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>414676</t>
+          <t>414365</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>614587</t>
+          <t>613727</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>669562</t>
+          <t>669280</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>662417</t>
+          <t>660853</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>725308</t>
+          <t>726328</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1290956</t>
+          <t>1291856</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1376645</t>
+          <t>1376632</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>81413</t>
+          <t>82293</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>118182</t>
+          <t>118937</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>95874</t>
+          <t>99380</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>138021</t>
+          <t>140248</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>189522</t>
+          <t>189265</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>244788</t>
+          <t>246269</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20837</t>
+          <t>19952</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14385</t>
+          <t>13710</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>11262</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28964</t>
+          <t>30334</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24304</t>
+          <t>24293</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49992</t>
+          <t>48581</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>52764</t>
+          <t>53367</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>85960</t>
+          <t>89710</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,47 +10908,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>103152</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>83985</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>125196</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>103152</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>85381</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>126855</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>376740</t>
+          <t>377076</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>453231</t>
+          <t>453253</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>405525</t>
+          <t>403934</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>487676</t>
+          <t>485546</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>803069</t>
+          <t>799815</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>917001</t>
+          <t>915049</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2114412</t>
+          <t>2110836</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2226493</t>
+          <t>2228949</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2169975</t>
+          <t>2175832</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2281977</t>
+          <t>2288180</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4315096</t>
+          <t>4317924</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4481713</t>
+          <t>4488531</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,9%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>703092</t>
+          <t>705924</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>801233</t>
+          <t>799437</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>730959</t>
+          <t>728698</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>831092</t>
+          <t>828102</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1460962</t>
+          <t>1461174</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1609353</t>
+          <t>1611092</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la calidad percibida del medioambiente de su barrio en 2023</t>
+          <t>Población según la calidad percibida del medioambiente de su barrio en 2023 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,97 +11659,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1669</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,04%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>291</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1422</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,02%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,13%</t>
         </is>
       </c>
     </row>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>414</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>13002</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31531</t>
+          <t>30311</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18235</t>
+          <t>17703</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35648</t>
+          <t>36507</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34379</t>
+          <t>35024</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59612</t>
+          <t>61016</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>333612</t>
+          <t>334734</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>386594</t>
+          <t>390352</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>394865</t>
+          <t>399857</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>496261</t>
+          <t>500793</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>751362</t>
+          <t>749755</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>857004</t>
+          <t>851861</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>62,67%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>225241</t>
+          <t>222324</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>280140</t>
+          <t>279722</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>206913</t>
+          <t>200411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>300895</t>
+          <t>296205</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>461013</t>
+          <t>462831</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>557887</t>
+          <t>558140</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,06%</t>
         </is>
       </c>
     </row>
@@ -12346,7 +12346,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>494</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8434</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10699</t>
+          <t>11491</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15495</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>18220</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55433</t>
+          <t>56061</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36517</t>
+          <t>35919</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60198</t>
+          <t>62315</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55282</t>
+          <t>56668</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>104983</t>
+          <t>103859</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>840699</t>
+          <t>837832</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1048457</t>
+          <t>1062341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>672407</t>
+          <t>671342</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>722093</t>
+          <t>722085</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1541887</t>
+          <t>1539086</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1797827</t>
+          <t>1794537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,57%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>119743</t>
+          <t>110331</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>293392</t>
+          <t>295672</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>187161</t>
+          <t>184554</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>231016</t>
+          <t>228995</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>288364</t>
+          <t>291186</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>499422</t>
+          <t>501480</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -13141,7 +13141,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>10238</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>438</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48633</t>
+          <t>49610</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>87667</t>
+          <t>89275</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38365</t>
+          <t>37960</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>106314</t>
+          <t>105011</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>93210</t>
+          <t>93640</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>175202</t>
+          <t>175411</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>515059</t>
+          <t>515291</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>567436</t>
+          <t>567597</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>660915</t>
+          <t>654986</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>834791</t>
+          <t>834689</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1198514</t>
+          <t>1204358</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1395291</t>
+          <t>1404412</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>73643</t>
+          <t>73152</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>115708</t>
+          <t>112253</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60918</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205893</t>
+          <t>216276</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>144294</t>
+          <t>139773</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>305368</t>
+          <t>295665</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16133</t>
+          <t>15064</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16526</t>
+          <t>16573</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9465</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25850</t>
+          <t>25806</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>11843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33012</t>
+          <t>30697</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18201</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37808</t>
+          <t>35195</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,47 +13868,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>45351</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>33559</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>60026</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>1,67%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>45351</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>33069</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>59653</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>104934</t>
+          <t>104146</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>150233</t>
+          <t>151110</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>120883</t>
+          <t>120189</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>173965</t>
+          <t>174923</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>238500</t>
+          <t>239161</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>307450</t>
+          <t>311041</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>654751</t>
+          <t>655349</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>713482</t>
+          <t>714861</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>804500</t>
+          <t>805811</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>883223</t>
+          <t>887408</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1478975</t>
+          <t>1476590</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1584788</t>
+          <t>1580886</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,48%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71675</t>
+          <t>71309</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>115500</t>
+          <t>115413</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>50796</t>
+          <t>52270</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>84989</t>
+          <t>87477</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>131698</t>
+          <t>131083</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>186163</t>
+          <t>186368</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18473</t>
+          <t>19802</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>18305</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13177</t>
+          <t>12447</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>31225</t>
+          <t>30876</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18226</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41034</t>
+          <t>43455</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14520,7 +14520,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25248</t>
+          <t>24772</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>46759</t>
+          <t>46669</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>47554</t>
+          <t>49244</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>79935</t>
+          <t>79409</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>189964</t>
+          <t>194959</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>287208</t>
+          <t>290968</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>242865</t>
+          <t>241354</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>335419</t>
+          <t>334605</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>473195</t>
+          <t>470116</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>606514</t>
+          <t>608797</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2416629</t>
+          <t>2418575</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2727479</t>
+          <t>2715354</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2597402</t>
+          <t>2608540</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2858580</t>
+          <t>2885695</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5068890</t>
+          <t>5065882</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5457860</t>
+          <t>5464645</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,34%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>501801</t>
+          <t>509264</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>729142</t>
+          <t>727247</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>562090</t>
+          <t>556185</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>750753</t>
+          <t>744420</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1151004</t>
+          <t>1152452</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1431237</t>
+          <t>1433226</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P05B-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>12864</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17381</t>
+          <t>18691</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>11219</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28674</t>
+          <t>28396</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20050</t>
+          <t>19704</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41360</t>
+          <t>40796</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46063</t>
+          <t>46339</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77200</t>
+          <t>75605</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61612</t>
+          <t>63091</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>93769</t>
+          <t>96660</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>115538</t>
+          <t>116543</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>160974</t>
+          <t>159382</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>514619</t>
+          <t>515317</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>557600</t>
+          <t>560496</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>482873</t>
+          <t>482745</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>528692</t>
+          <t>530806</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1012892</t>
+          <t>1012373</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1075549</t>
+          <t>1075835</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66037</t>
+          <t>65447</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101230</t>
+          <t>100292</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65894</t>
+          <t>67219</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>101010</t>
+          <t>101743</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144913</t>
+          <t>143056</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>193244</t>
+          <t>191613</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8502</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15246</t>
+          <t>14516</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12098</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30305</t>
+          <t>30744</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27793</t>
+          <t>27248</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51962</t>
+          <t>51389</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42855</t>
+          <t>43228</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72975</t>
+          <t>74156</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>143855</t>
+          <t>145994</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>195062</t>
+          <t>192617</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>137780</t>
+          <t>136547</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184720</t>
+          <t>185665</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>298829</t>
+          <t>297218</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>363031</t>
+          <t>361676</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>609138</t>
+          <t>608104</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>672582</t>
+          <t>669770</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>618995</t>
+          <t>616594</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>677747</t>
+          <t>678115</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1245293</t>
+          <t>1246236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1329969</t>
+          <t>1328694</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,9%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>105457</t>
+          <t>108729</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153965</t>
+          <t>153838</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95355</t>
+          <t>95713</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137907</t>
+          <t>137855</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>215436</t>
+          <t>215407</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>279866</t>
+          <t>280653</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>15810</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>806</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8891</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17045</t>
+          <t>17383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20101</t>
+          <t>19934</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15704</t>
+          <t>15353</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34671</t>
+          <t>34829</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23667</t>
+          <t>24789</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48701</t>
+          <t>48372</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>138092</t>
+          <t>136910</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>181810</t>
+          <t>181197</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>137886</t>
+          <t>137089</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>181400</t>
+          <t>182564</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>286802</t>
+          <t>285271</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>349746</t>
+          <t>349987</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>427116</t>
+          <t>426827</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>476337</t>
+          <t>476560</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>416071</t>
+          <t>415269</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>465402</t>
+          <t>465187</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>858375</t>
+          <t>856389</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>928289</t>
+          <t>929840</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,25%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40328</t>
+          <t>38712</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68143</t>
+          <t>66741</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44196</t>
+          <t>42857</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72750</t>
+          <t>71035</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>88470</t>
+          <t>91333</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>129530</t>
+          <t>131894</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>17636</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18212</t>
+          <t>19042</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>11804</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29901</t>
+          <t>30187</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24118</t>
+          <t>22790</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45967</t>
+          <t>46345</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>45474</t>
+          <t>45762</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>73082</t>
+          <t>77036</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>73911</t>
+          <t>74327</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>111083</t>
+          <t>112873</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>250753</t>
+          <t>248133</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>303871</t>
+          <t>303540</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>278366</t>
+          <t>281037</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>340687</t>
+          <t>339650</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>547346</t>
+          <t>545742</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>626801</t>
+          <t>627055</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>499885</t>
+          <t>498878</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>560175</t>
+          <t>558887</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>558661</t>
+          <t>558317</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>624272</t>
+          <t>622659</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1074080</t>
+          <t>1075583</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1161149</t>
+          <t>1163629</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,84%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>72430</t>
+          <t>73185</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>108038</t>
+          <t>108761</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54058</t>
+          <t>57213</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>86488</t>
+          <t>88606</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>136911</t>
+          <t>138221</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>184218</t>
+          <t>187218</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12211</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>32611</t>
+          <t>33738</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12865</t>
+          <t>13099</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30036</t>
+          <t>30498</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>30041</t>
+          <t>29310</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>58166</t>
+          <t>56316</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>58566</t>
+          <t>60476</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>95655</t>
+          <t>95098</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>116553</t>
+          <t>115043</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>160354</t>
+          <t>163137</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>185225</t>
+          <t>185308</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>243605</t>
+          <t>242265</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>621924</t>
+          <t>618840</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>712896</t>
+          <t>709068</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>657519</t>
+          <t>659971</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>752487</t>
+          <t>750993</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1304224</t>
+          <t>1306335</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1437931</t>
+          <t>1433301</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2098637</t>
+          <t>2102092</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2206359</t>
+          <t>2209529</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2135263</t>
+          <t>2132902</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2246005</t>
+          <t>2245206</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4267314</t>
+          <t>4268385</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4424225</t>
+          <t>4424624</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,54%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>318544</t>
+          <t>323105</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>391800</t>
+          <t>391780</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>293614</t>
+          <t>295168</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>361689</t>
+          <t>364175</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>635306</t>
+          <t>633860</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>733809</t>
+          <t>734071</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6140</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>7432</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20717</t>
+          <t>20716</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42348</t>
+          <t>42440</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38235</t>
+          <t>36791</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67207</t>
+          <t>65912</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63125</t>
+          <t>63688</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>99047</t>
+          <t>99019</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>501393</t>
+          <t>503979</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>548242</t>
+          <t>548950</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>479467</t>
+          <t>480382</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>529334</t>
+          <t>528235</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>998300</t>
+          <t>1001436</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1062491</t>
+          <t>1068359</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,4%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>124130</t>
+          <t>123723</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>168968</t>
+          <t>167111</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>115080</t>
+          <t>115662</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>158585</t>
+          <t>157805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>251985</t>
+          <t>250828</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>313564</t>
+          <t>313240</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14608</t>
+          <t>13515</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11860</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>20049</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19600</t>
+          <t>19677</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>12435</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32202</t>
+          <t>32224</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21928</t>
+          <t>22888</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45943</t>
+          <t>47859</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>104165</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>149855</t>
+          <t>149664</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108467</t>
+          <t>107377</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>152341</t>
+          <t>152421</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>220625</t>
+          <t>221206</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>285011</t>
+          <t>284836</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>756340</t>
+          <t>757500</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>813146</t>
+          <t>812046</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>762658</t>
+          <t>761412</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>820478</t>
+          <t>819557</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1539829</t>
+          <t>1539612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1619559</t>
+          <t>1619704</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70625</t>
+          <t>69354</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108089</t>
+          <t>106530</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63757</t>
+          <t>63049</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>99757</t>
+          <t>99329</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142110</t>
+          <t>141356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>192929</t>
+          <t>193491</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>496</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>24362</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12441</t>
+          <t>12670</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31072</t>
+          <t>32332</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>93623</t>
+          <t>91387</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>134627</t>
+          <t>133110</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>97937</t>
+          <t>100194</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>140608</t>
+          <t>141113</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>201108</t>
+          <t>203899</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>259531</t>
+          <t>265685</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>500941</t>
+          <t>500627</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>554063</t>
+          <t>555283</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>527070</t>
+          <t>527135</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>577559</t>
+          <t>581338</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1048359</t>
+          <t>1048587</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1120447</t>
+          <t>1118506</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,98%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>82596</t>
+          <t>82092</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>120759</t>
+          <t>122510</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75949</t>
+          <t>75157</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>112093</t>
+          <t>114688</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>167663</t>
+          <t>168000</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>220392</t>
+          <t>224904</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>14093</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14698</t>
+          <t>14231</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10711</t>
+          <t>10372</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27440</t>
+          <t>28388</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11401</t>
+          <t>10645</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30385</t>
+          <t>27662</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25019</t>
+          <t>24942</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49328</t>
+          <t>49818</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>174019</t>
+          <t>174974</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>225527</t>
+          <t>224190</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>217077</t>
+          <t>220525</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>276161</t>
+          <t>275632</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>410333</t>
+          <t>409522</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>485974</t>
+          <t>484387</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>636606</t>
+          <t>638591</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>692004</t>
+          <t>693382</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>688114</t>
+          <t>688455</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>749019</t>
+          <t>747552</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1341210</t>
+          <t>1345050</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1425471</t>
+          <t>1426917</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,01%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>36927</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>63618</t>
+          <t>63070</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>43186</t>
+          <t>41571</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>74593</t>
+          <t>72078</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>87428</t>
+          <t>88993</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>128348</t>
+          <t>127074</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>7621</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>25106</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17139</t>
+          <t>17343</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14894</t>
+          <t>15130</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35986</t>
+          <t>36187</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>30687</t>
+          <t>29899</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>57748</t>
+          <t>55782</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34733</t>
+          <t>35420</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>63108</t>
+          <t>64238</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>71454</t>
+          <t>73060</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>110045</t>
+          <t>114944</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>422877</t>
+          <t>425458</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>508314</t>
+          <t>508395</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>503120</t>
+          <t>501583</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>593096</t>
+          <t>590698</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>953770</t>
+          <t>950724</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1073676</t>
+          <t>1075181</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2458595</t>
+          <t>2455346</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2560733</t>
+          <t>2559670</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2516948</t>
+          <t>2520176</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2624898</t>
+          <t>2626494</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4999756</t>
+          <t>5002219</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5157851</t>
+          <t>5152308</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,09%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>345977</t>
+          <t>344201</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>420491</t>
+          <t>420148</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>330394</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>408657</t>
+          <t>405572</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>693919</t>
+          <t>699778</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>801413</t>
+          <t>806041</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>940</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10774</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>941</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>9496</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13509</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17453</t>
+          <t>16246</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21579</t>
+          <t>21865</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45379</t>
+          <t>45424</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28757</t>
+          <t>28369</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>53036</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56785</t>
+          <t>55519</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>92084</t>
+          <t>90110</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>363826</t>
+          <t>366379</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>416872</t>
+          <t>416774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>370133</t>
+          <t>371769</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>424933</t>
+          <t>423899</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>754847</t>
+          <t>753393</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>828794</t>
+          <t>825182</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,38%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>217227</t>
+          <t>217952</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>268134</t>
+          <t>268696</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>204932</t>
+          <t>207012</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>254871</t>
+          <t>254086</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>435235</t>
+          <t>438010</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>504218</t>
+          <t>507104</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>7608</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>971</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>18595</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9580</t>
+          <t>9413</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26450</t>
+          <t>26258</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17618</t>
+          <t>17124</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39846</t>
+          <t>39839</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69440</t>
+          <t>69460</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>106084</t>
+          <t>107372</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74900</t>
+          <t>74615</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>110788</t>
+          <t>112312</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>154152</t>
+          <t>154271</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>208178</t>
+          <t>206124</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>644383</t>
+          <t>645325</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>710049</t>
+          <t>709920</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>641510</t>
+          <t>639090</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>703694</t>
+          <t>700028</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1302362</t>
+          <t>1308639</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1394589</t>
+          <t>1392269</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,54%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214825</t>
+          <t>217880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>273978</t>
+          <t>272410</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>229104</t>
+          <t>229870</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>285941</t>
+          <t>287212</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>463146</t>
+          <t>464812</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>544916</t>
+          <t>543997</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9190</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>11447</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17620</t>
+          <t>17919</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15884</t>
+          <t>15219</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36196</t>
+          <t>35854</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21922</t>
+          <t>22441</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45362</t>
+          <t>47455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>93808</t>
+          <t>96926</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>138262</t>
+          <t>139386</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>97071</t>
+          <t>98382</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>137204</t>
+          <t>138537</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>205483</t>
+          <t>206878</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>261682</t>
+          <t>263815</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>436006</t>
+          <t>434792</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>491424</t>
+          <t>491048</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>434407</t>
+          <t>437725</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>489921</t>
+          <t>491487</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>889256</t>
+          <t>894880</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>966259</t>
+          <t>968395</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>143439</t>
+          <t>143839</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192309</t>
+          <t>191051</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>152872</t>
+          <t>152694</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>202247</t>
+          <t>200294</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>309026</t>
+          <t>309722</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>375986</t>
+          <t>375862</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8822</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9980</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14217</t>
+          <t>14476</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17666</t>
+          <t>18251</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15709</t>
+          <t>15136</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37233</t>
+          <t>35537</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>24551</t>
+          <t>23225</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48468</t>
+          <t>47834</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>156907</t>
+          <t>155058</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>203977</t>
+          <t>202230</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>171230</t>
+          <t>170979</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>224167</t>
+          <t>226067</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>339454</t>
+          <t>342457</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>414365</t>
+          <t>416461</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>613727</t>
+          <t>610574</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>669280</t>
+          <t>668618</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>660853</t>
+          <t>661265</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>726328</t>
+          <t>724943</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1291856</t>
+          <t>1293736</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1376632</t>
+          <t>1376806</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>82293</t>
+          <t>81952</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>118937</t>
+          <t>118443</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>99380</t>
+          <t>97970</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>140248</t>
+          <t>140430</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>189265</t>
+          <t>192027</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>246269</t>
+          <t>249860</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>19728</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,82 +10760,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>3092</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>13881</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>18317</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>10879</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>29181</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>7102</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2969</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>13710</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>18317</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>11262</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>30334</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24293</t>
+          <t>23846</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>48581</t>
+          <t>48690</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>53367</t>
+          <t>52240</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>89710</t>
+          <t>86095</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>83985</t>
+          <t>83993</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>125196</t>
+          <t>126841</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>377076</t>
+          <t>375475</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>453253</t>
+          <t>458740</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>403934</t>
+          <t>406851</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>485546</t>
+          <t>487352</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>799815</t>
+          <t>800726</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>915049</t>
+          <t>917343</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2110836</t>
+          <t>2118074</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2228949</t>
+          <t>2232256</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2175832</t>
+          <t>2174583</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2288180</t>
+          <t>2292787</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4317924</t>
+          <t>4320492</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4488531</t>
+          <t>4490618</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,93%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>705924</t>
+          <t>696362</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>799437</t>
+          <t>800827</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>728698</t>
+          <t>729027</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>828102</t>
+          <t>831987</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1461174</t>
+          <t>1465012</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1611092</t>
+          <t>1606973</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>278</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>278</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
     </row>
@@ -11767,7 +11767,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,17 +11802,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>432</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20486</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13002</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30311</t>
+          <t>34802</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25441</t>
+          <t>27344</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17703</t>
+          <t>19717</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36507</t>
+          <t>38893</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>45927</t>
+          <t>49863</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35024</t>
+          <t>38562</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61016</t>
+          <t>66431</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -11993,32 +11993,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>362062</t>
+          <t>388614</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>334734</t>
+          <t>362362</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>390352</t>
+          <t>417617</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>427228</t>
+          <t>409530</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>399857</t>
+          <t>385933</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>500793</t>
+          <t>430289</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>789290</t>
+          <t>798143</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>749755</t>
+          <t>760002</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>851861</t>
+          <t>830999</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>250472</t>
+          <t>277033</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>222324</t>
+          <t>248212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>279722</t>
+          <t>303569</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>270237</t>
+          <t>294867</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>200411</t>
+          <t>273875</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>296205</t>
+          <t>317197</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>520709</t>
+          <t>571900</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>462831</t>
+          <t>540229</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>558140</t>
+          <t>607920</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>724939</t>
+          <t>733782</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>724939</t>
+          <t>733782</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>724939</t>
+          <t>733782</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1359361</t>
+          <t>1423405</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1359361</t>
+          <t>1423405</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1359361</t>
+          <t>1423405</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,17 +12406,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>750</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>5574</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11491</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>8849</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37932</t>
+          <t>39162</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18220</t>
+          <t>27571</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56061</t>
+          <t>53671</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,32 +12597,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>53242</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35919</t>
+          <t>41814</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62315</t>
+          <t>67549</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>84339</t>
+          <t>92404</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>56668</t>
+          <t>75788</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>103859</t>
+          <t>110584</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>923229</t>
+          <t>749802</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>837832</t>
+          <t>713860</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1062341</t>
+          <t>783543</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>697713</t>
+          <t>781211</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>671342</t>
+          <t>755621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>722085</t>
+          <t>808349</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1620942</t>
+          <t>1531012</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1539086</t>
+          <t>1491840</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1794537</t>
+          <t>1574611</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>74,41%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>224130</t>
+          <t>252564</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110331</t>
+          <t>220574</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>295672</t>
+          <t>287035</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,32 +12823,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>206816</t>
+          <t>228923</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>184554</t>
+          <t>204479</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>228995</t>
+          <t>253975</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>430947</t>
+          <t>481486</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>291186</t>
+          <t>443445</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>501480</t>
+          <t>521452</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1189982</t>
+          <t>1046094</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1189982</t>
+          <t>1046094</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1189982</t>
+          <t>1046094</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>957456</t>
+          <t>1070098</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>957456</t>
+          <t>1070098</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>957456</t>
+          <t>1070098</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2147438</t>
+          <t>2116192</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2147438</t>
+          <t>2116192</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2147438</t>
+          <t>2116192</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5044</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>667</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -13098,12 +13098,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5624</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>880</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10238</t>
+          <t>11039</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>723</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>13826</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>65783</t>
+          <t>72486</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49610</t>
+          <t>54069</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>89275</t>
+          <t>94974</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>74533</t>
+          <t>85014</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37960</t>
+          <t>68424</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>105011</t>
+          <t>103243</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>140316</t>
+          <t>157500</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>93640</t>
+          <t>131991</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>175411</t>
+          <t>184785</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>542838</t>
+          <t>615003</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>515291</t>
+          <t>585064</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>567597</t>
+          <t>640940</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,67 +13392,67 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>740729</t>
+          <t>626043</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>654986</t>
+          <t>601293</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>834689</t>
+          <t>649030</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
+          <t>77,07%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>74,03%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>79,9%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1241045</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>1207747</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>1280436</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>76,92%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>74,85%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>79,36%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>70,17%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>89,43%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1283566</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>1204358</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1404412</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>78,4%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>73,56%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -13470,32 +13470,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>91291</t>
+          <t>108878</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>73152</t>
+          <t>88838</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>112253</t>
+          <t>134257</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>115296</t>
+          <t>97771</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>81805</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>216276</t>
+          <t>118491</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>206588</t>
+          <t>206649</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>139773</t>
+          <t>179694</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>295665</t>
+          <t>238492</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>703912</t>
+          <t>801201</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>703912</t>
+          <t>801201</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>703912</t>
+          <t>801201</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1637277</t>
+          <t>1613459</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1637277</t>
+          <t>1613459</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1637277</t>
+          <t>1613459</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15064</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>8798</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16573</t>
+          <t>15746</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>15774</t>
+          <t>15788</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9345</t>
+          <t>9785</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25806</t>
+          <t>25291</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>19984</t>
+          <t>20021</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11843</t>
+          <t>12438</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30697</t>
+          <t>31802</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>25367</t>
+          <t>26611</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17324</t>
+          <t>18695</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>35195</t>
+          <t>36552</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>45351</t>
+          <t>46632</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>33559</t>
+          <t>34434</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>60026</t>
+          <t>60862</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>124689</t>
+          <t>134035</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>104146</t>
+          <t>112766</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>151110</t>
+          <t>158741</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>150154</t>
+          <t>165099</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>120189</t>
+          <t>144858</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>174923</t>
+          <t>186524</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>274843</t>
+          <t>299135</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>239161</t>
+          <t>270270</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>311041</t>
+          <t>332783</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>685064</t>
+          <t>733717</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>655349</t>
+          <t>704991</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>714861</t>
+          <t>763197</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>836401</t>
+          <t>839202</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>805811</t>
+          <t>813101</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>887408</t>
+          <t>865577</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1521465</t>
+          <t>1572920</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1476590</t>
+          <t>1529730</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1580886</t>
+          <t>1611955</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>76,78%</t>
         </is>
       </c>
     </row>
@@ -14152,32 +14152,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>89210</t>
+          <t>93036</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71309</t>
+          <t>75398</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>115413</t>
+          <t>119024</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>67705</t>
+          <t>71856</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52270</t>
+          <t>57440</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>87477</t>
+          <t>87599</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,32 +14222,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>156915</t>
+          <t>164892</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>131083</t>
+          <t>140035</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>186368</t>
+          <t>195009</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>926034</t>
+          <t>987799</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>926034</t>
+          <t>987799</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>926034</t>
+          <t>987799</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1088313</t>
+          <t>1111567</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1088313</t>
+          <t>1111567</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1088313</t>
+          <t>1111567</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2014347</t>
+          <t>2099367</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2014347</t>
+          <t>2099367</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2014347</t>
+          <t>2099367</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,97 +14382,97 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>9525</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19802</t>
+          <t>17936</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>10892</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>6254</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>18426</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>20215</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>12748</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>30854</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>10655</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>6007</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>18305</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>20180</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>12447</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>30876</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>27640</t>
+          <t>28545</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18327</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>43455</t>
+          <t>41925</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>34759</t>
+          <t>36712</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24772</t>
+          <t>27098</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>46669</t>
+          <t>48221</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>62399</t>
+          <t>65257</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>49244</t>
+          <t>51573</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>79409</t>
+          <t>81766</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>248889</t>
+          <t>268203</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>194959</t>
+          <t>236224</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>290968</t>
+          <t>304252</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>296535</t>
+          <t>330699</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>241354</t>
+          <t>297604</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>334605</t>
+          <t>362932</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>545425</t>
+          <t>598902</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>470116</t>
+          <t>549682</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>608797</t>
+          <t>646065</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2513192</t>
+          <t>2487135</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2418575</t>
+          <t>2423307</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2715354</t>
+          <t>2550642</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2702071</t>
+          <t>2655986</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2608540</t>
+          <t>2608477</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2885695</t>
+          <t>2703906</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>5215263</t>
+          <t>5143121</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5065882</t>
+          <t>5064366</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5464645</t>
+          <t>5219065</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>71,96%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>655103</t>
+          <t>731512</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>509264</t>
+          <t>677198</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>727247</t>
+          <t>786614</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>660054</t>
+          <t>693416</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>556185</t>
+          <t>652977</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>744420</t>
+          <t>739247</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1315157</t>
+          <t>1424928</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1152452</t>
+          <t>1358338</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1433226</t>
+          <t>1500706</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3454349</t>
+          <t>3524718</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3454349</t>
+          <t>3524718</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3454349</t>
+          <t>3524718</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3704074</t>
+          <t>3727706</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3704074</t>
+          <t>3727706</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3704074</t>
+          <t>3727706</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7158423</t>
+          <t>7252424</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7158423</t>
+          <t>7252424</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7158423</t>
+          <t>7252424</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
